--- a/_build/download/trabajadores.xlsx
+++ b/_build/download/trabajadores.xlsx
@@ -115,10 +115,10 @@
     </r>
   </si>
   <si>
-    <t>Los nombres de las empresas y sus sedes se han inspirado en distintas fuentes de la filmografía de ciencia ficción,</t>
-  </si>
-  <si>
-    <t>con intereses puramente didácticos.</t>
+    <t>Algunos nombres de compañías, sedes y personajes se inspiran en sagas de ciencia ficción y se usan solo como homenaje, con fines creativos y didácticos,</t>
+  </si>
+  <si>
+    <t>sin relación con sus titulares ni respaldo por su parte. Aviso completo en el capítulo «Licencia» de los libros del universo R-Stars.</t>
   </si>
   <si>
     <t>* Imagen generada con IA.</t>
